--- a/DB/backup.xlsx
+++ b/DB/backup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="work_goal" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="work_done" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="result" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="work_goal" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="work_done" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="result" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,18 +665,10 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -704,18 +696,10 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -743,18 +727,10 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -782,18 +758,10 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
@@ -821,18 +789,10 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -860,18 +820,10 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
@@ -899,18 +851,10 @@
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
@@ -938,18 +882,10 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
@@ -977,18 +913,10 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
@@ -1016,18 +944,10 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
@@ -1055,18 +975,10 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
@@ -1094,18 +1006,10 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>(1970.0,1100.0)</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.320m</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">

--- a/DB/backup.xlsx
+++ b/DB/backup.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -691,7 +691,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -753,7 +753,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -877,7 +877,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -908,7 +908,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -970,7 +970,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1L_cylinder</t>
+          <t>20mL_cylinder</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
